--- a/reports/eps_daily_2026-05-07.xlsx
+++ b/reports/eps_daily_2026-05-07.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,16 +33,26 @@
     <font>
       <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="00FFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="00B45F06"/>
-      <sz val="12"/>
+      <color rgb="00C00000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
@@ -51,24 +61,34 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="12"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
-      <b val="1"/>
-      <color rgb="00B45F06"/>
-      <sz val="14"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
-      <b val="1"/>
-      <color rgb="0038761D"/>
-      <sz val="14"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,17 +97,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="002F5496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,22 +152,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,199 +568,226 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>📊 EPS 日報 2026-05-07</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>今日新公告</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
+          <t>🆕 今日新公告</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>3 檔</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>評分 ≥ 8 高度超預期</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
+          <t>🔥 評分 ≥ 8 高度超預期</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2 檔</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>評分 6-7 值得關注</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
+          <t>⭐ 評分 6-7 值得關注</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2 檔</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>評分 ≤ -4 衰退警示</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
+          <t>⚠️ 評分 ≤ -4 衰退警示</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>0 檔</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>全市場分析筆數</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+          <t>📊 全市場分析筆數</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>5 檔</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>🏆 已確認 2026Q1 EPS 已贏 2025 全年 (1 檔)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>2026Q1 / 2025全年</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>倍數</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>評分</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>評分理由</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>8.41 / 2.13 = 3.95x</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>3.95x</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>YoY 轉虧為盈+1435%、Q1 一季賺贏全年 3.9 倍、本業強勁驅動</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>YoY轉虧為盈+1435%、Q1累計達成率395%、本業強勁</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>📊 觀察重點</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>• 共 3 檔有 2026Q1 EPS 資料；其中 +8 以上 1 檔、+6~7 2 檔、+4~5 0 檔</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>• 2026Q1 EPS 最高三名：雙鴻 12.61、南亞科 8.41、均華 5.19</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>• 已確認 2026Q1 一季賺贏 2025 全年 1 檔（含虧轉盈）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>FinMind API (https://finmindtrade.com)</t>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>FinMind API + Anthropic Claude Haiku</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>產出時間</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-05-07 22:45:49</t>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07 23:03:35</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="13">
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="C4:F4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B18:F18"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C5:F5"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -708,362 +801,372 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🆕 今日新公告 (3 檔)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>最新季</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>去年同季 EPS</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>去年同季</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>YoY %</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>YoY Δ</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>累計 EPS</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>去年全年</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>達成率 %</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>達成率</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>QoQ %</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>驚喜分數</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>評分</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>級別</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>評分理由</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>GM%</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>OPM%</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>業外%</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E3" s="8" t="n">
         <v>8.41</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F3" s="8" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>+1434.9%</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H3" s="8" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I3" s="8" t="n">
         <v>8.41</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J3" s="8" t="n">
         <v>2.13</v>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>394.8%</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>+134.9%</t>
         </is>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="M3" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>YoY 轉虧為盈+1435%、Q1 一季賺贏全年 3.9 倍、本業強勁驅動</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t>YoY轉虧為盈+1435%、Q1累計達成率395%、本業強勁</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="inlineStr">
         <is>
           <t>67.9%</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>61.3%</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>6.2%</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>3324</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E4" s="13" t="n">
         <v>12.61</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F4" s="13" t="n">
         <v>5.66</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>+122.8%</t>
         </is>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H4" s="13" t="n">
         <v>6.95</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I4" s="13" t="n">
         <v>12.61</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="J4" s="13" t="n">
         <v>28.2</v>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>+24.5%</t>
         </is>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M4" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>YoY 大增+123%、本業驅動、單季表現穩健但累計進度正常</t>
-        </is>
-      </c>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>YoY大增+123%、本業驅動穩健但累計進度正常</t>
+        </is>
+      </c>
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>29.7%</t>
         </is>
       </c>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="Q4" s="13" t="inlineStr">
         <is>
           <t>17.8%</t>
         </is>
       </c>
-      <c r="R3" s="7" t="inlineStr">
+      <c r="R4" s="13" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>均華</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E5" s="13" t="n">
         <v>5.19</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F5" s="13" t="n">
         <v>1.64</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>+216.5%</t>
         </is>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H5" s="13" t="n">
         <v>3.55</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I5" s="13" t="n">
         <v>5.19</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J5" s="13" t="n">
         <v>12.75</v>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>40.7%</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>+54.9%</t>
         </is>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M5" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>YoY 大幅成長 216%、本業驅動、累計進度符合預期</t>
-        </is>
-      </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="O5" s="14" t="inlineStr">
+        <is>
+          <t>YoY大增216%、本業驅動但累計進度正常</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>44.9%</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="Q5" s="13" t="inlineStr">
         <is>
           <t>21.7%</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>4.7%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
 </worksheet>
@@ -1078,102 +1181,109 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>🏆 已確認 2026Q1 EPS &gt; 2025 全年 EPS (1 檔)</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>一季賺贏去年全年的明星標的（含去年虧損 → 今年轉盈）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>2026Q1 EPS</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>2025Q1 EPS</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>2025 全年 EPS</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>累計/全年</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>倍數</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>驚喜分數</t>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>評分</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="8" t="n">
         <v>8.41</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="8" t="n">
         <v>-0.63</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="8" t="n">
         <v>2.13</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>394.8%</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>3.95x</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="8" t="n">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1190,180 +1300,187 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>💰 2026Q1 EPS 高低排行（前 3 名）</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>依當期 EPS 由高到低；達成率 ≥ 100% 整列鮮黃高亮（已贏全年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>驚喜分數</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>評分</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>2026Q1 EPS</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>上季 EPS</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>QoQ Δ</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>去年全年 EPS</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>累計達成率</t>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>達成率</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>3324</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="17" t="n">
         <v>12.61</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="17" t="n">
         <v>10.13</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="17" t="n">
         <v>2.48</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="17" t="n">
         <v>28.2</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="8" t="n">
         <v>8.41</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="8" t="n">
         <v>3.58</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="8" t="n">
         <v>4.83</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="8" t="n">
         <v>2.13</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>395%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>均華</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="17" t="n">
         <v>5.19</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="17" t="n">
         <v>3.35</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="17" t="n">
         <v>1.84</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="17" t="n">
         <v>12.75</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1376,522 +1493,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>🔥 高分排行 (評分 ≥ 4，5 檔)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>最新季</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>去年同季 EPS</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>去年同季</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>YoY %</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>YoY Δ</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>累計 EPS</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>去年全年</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>達成率 %</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>達成率</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>QoQ %</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>驚喜分數</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>評分</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>級別</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>評分理由</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>GM%</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>OPM%</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>業外%</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>5386</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>2025Q4</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E3" s="8" t="n">
         <v>5.58</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F3" s="8" t="n">
         <v>1.83</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>+204.9%</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H3" s="8" t="n">
         <v>3.75</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I3" s="8" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J3" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>258.2%</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>+758.5%</t>
         </is>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="M3" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>QoQ 爆發 +758%、YoY 爆發 +205%、已賺贏去年全年 (258%)</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P3" s="8" t="inlineStr">
         <is>
           <t>13.4%</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>10.4%</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>-6.0%</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E4" s="8" t="n">
         <v>8.41</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F4" s="8" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>+1434.9%</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H4" s="8" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I4" s="8" t="n">
         <v>8.41</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J4" s="8" t="n">
         <v>2.13</v>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>394.8%</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>+134.9%</t>
         </is>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M4" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>YoY 轉虧為盈+1435%、Q1 一季賺贏全年 3.9 倍、本業強勁驅動</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>YoY轉虧為盈+1435%、Q1累計達成率395%、本業強勁</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>67.9%</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>61.3%</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>6.2%</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>3324</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E5" s="13" t="n">
         <v>12.61</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F5" s="13" t="n">
         <v>5.66</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>+122.8%</t>
         </is>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H5" s="13" t="n">
         <v>6.95</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I5" s="13" t="n">
         <v>12.61</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J5" s="13" t="n">
         <v>28.2</v>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>+24.5%</t>
         </is>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M5" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>YoY 大增+123%、本業驅動、單季表現穩健但累計進度正常</t>
-        </is>
-      </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="O5" s="14" t="inlineStr">
+        <is>
+          <t>YoY大增+123%、本業驅動穩健但累計進度正常</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>29.7%</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="Q5" s="13" t="inlineStr">
         <is>
           <t>17.8%</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>均華</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E6" s="13" t="n">
         <v>5.19</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F6" s="13" t="n">
         <v>1.64</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>+216.5%</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H6" s="13" t="n">
         <v>3.55</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I6" s="13" t="n">
         <v>5.19</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J6" s="13" t="n">
         <v>12.75</v>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>40.7%</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>+54.9%</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M6" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>YoY 大幅成長 216%、本業驅動、累計進度符合預期</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr">
+        <is>
+          <t>YoY大增216%、本業驅動但累計進度正常</t>
+        </is>
+      </c>
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t>44.9%</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t>21.7%</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="R6" s="13" t="inlineStr">
         <is>
           <t>4.7%</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>2330</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>2025Q4</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E7" s="13" t="n">
         <v>19.51</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F7" s="13" t="n">
         <v>14.45</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>+35.0%</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H7" s="13" t="n">
         <v>5.06</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I7" s="13" t="n">
         <v>66.26000000000001</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J7" s="13" t="n">
         <v>45.26</v>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>146.4%</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>+11.9%</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M7" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t>有亮點待觀察</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t>YoY +35%、已賺贏去年全年 (146%)、OPM 54% 強</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t>62.3%</t>
         </is>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="Q7" s="13" t="inlineStr">
         <is>
           <t>54.0%</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr">
+      <c r="R7" s="13" t="inlineStr">
         <is>
           <t>5.4%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
 </worksheet>
@@ -1903,522 +2030,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>📊 完整 EPS 全市場 (5 檔)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>最新季</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>去年同季 EPS</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>去年同季</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>YoY %</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>YoY Δ</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>累計 EPS</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>去年全年</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>達成率 %</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>達成率</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>QoQ %</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>驚喜分數</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>評分</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>級別</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>評分理由</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>GM%</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>OPM%</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>業外%</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>5386</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>2025Q4</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E3" s="8" t="n">
         <v>5.58</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F3" s="8" t="n">
         <v>1.83</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>+204.9%</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H3" s="8" t="n">
         <v>3.75</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I3" s="8" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J3" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>258.2%</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>+758.5%</t>
         </is>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="M3" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>QoQ 爆發 +758%、YoY 爆發 +205%、已賺贏去年全年 (258%)</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P3" s="8" t="inlineStr">
         <is>
           <t>13.4%</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>10.4%</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>-6.0%</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E4" s="8" t="n">
         <v>8.41</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F4" s="8" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>+1434.9%</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H4" s="8" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I4" s="8" t="n">
         <v>8.41</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J4" s="8" t="n">
         <v>2.13</v>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>394.8%</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>+134.9%</t>
         </is>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M4" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>YoY 轉虧為盈+1435%、Q1 一季賺贏全年 3.9 倍、本業強勁驅動</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>YoY轉虧為盈+1435%、Q1累計達成率395%、本業強勁</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>67.9%</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>61.3%</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>6.2%</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>3324</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E5" s="13" t="n">
         <v>12.61</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F5" s="13" t="n">
         <v>5.66</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>+122.8%</t>
         </is>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H5" s="13" t="n">
         <v>6.95</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I5" s="13" t="n">
         <v>12.61</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J5" s="13" t="n">
         <v>28.2</v>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>+24.5%</t>
         </is>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M5" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>YoY 大增+123%、本業驅動、單季表現穩健但累計進度正常</t>
-        </is>
-      </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="O5" s="14" t="inlineStr">
+        <is>
+          <t>YoY大增+123%、本業驅動穩健但累計進度正常</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>29.7%</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="Q5" s="13" t="inlineStr">
         <is>
           <t>17.8%</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>均華</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E6" s="13" t="n">
         <v>5.19</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F6" s="13" t="n">
         <v>1.64</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>+216.5%</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H6" s="13" t="n">
         <v>3.55</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I6" s="13" t="n">
         <v>5.19</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J6" s="13" t="n">
         <v>12.75</v>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>40.7%</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>+54.9%</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M6" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>YoY 大幅成長 216%、本業驅動、累計進度符合預期</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr">
+        <is>
+          <t>YoY大增216%、本業驅動但累計進度正常</t>
+        </is>
+      </c>
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t>44.9%</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t>21.7%</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="R6" s="13" t="inlineStr">
         <is>
           <t>4.7%</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>2330</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>2025Q4</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E7" s="13" t="n">
         <v>19.51</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F7" s="13" t="n">
         <v>14.45</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>+35.0%</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H7" s="13" t="n">
         <v>5.06</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I7" s="13" t="n">
         <v>66.26000000000001</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J7" s="13" t="n">
         <v>45.26</v>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>146.4%</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>+11.9%</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M7" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t>有亮點待觀察</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t>YoY +35%、已賺贏去年全年 (146%)、OPM 54% 強</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t>62.3%</t>
         </is>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="Q7" s="13" t="inlineStr">
         <is>
           <t>54.0%</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr">
+      <c r="R7" s="13" t="inlineStr">
         <is>
           <t>5.4%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
 </worksheet>

--- a/reports/eps_daily_2026-05-07.xlsx
+++ b/reports/eps_daily_2026-05-07.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,15 +38,9 @@
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft JhengHei"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="14"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
@@ -73,6 +67,17 @@
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
@@ -88,7 +93,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -98,11 +103,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -117,16 +117,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00548235"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,56 +143,103 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -565,230 +607,307 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 EPS 日報 2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>🆕 今日新公告</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>3 檔</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="F3" s="5" t="n"/>
+          <t>2026Q1 EPS 日報 vs 2025 比較整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>資料來源：FinMind API (5 檔分析、3 檔今日新公告)　|　日期：2026-05-07　|　AI 評分 by Claude Haiku 4.5</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>🔥 評分 ≥ 8 高度超預期</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>2 檔</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="F4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>⭐ 評分 6-7 值得關注</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2 檔</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 評分 ≤ -4 衰退警示</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>0 檔</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="F6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>📊 全市場分析筆數</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>5 檔</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="F7" s="5" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>🏆 已確認 2026Q1 EPS 已贏 2025 全年 (1 檔)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026Q1 / 2025全年</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>倍數</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>評分</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>重點</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>8.41 / 2.13 = 3.95x</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>3.95x</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>YoY+1435%轉虧為盈、Q1一季賺贏全年4倍、本業驅動毛利67.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>📊 重要觀察</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>共 3 檔有完整 EPS 資料；高分分布：+9 分 1 檔、+7 分 1 檔、+6 分 1 檔</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>2026Q1 / 2025全年</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>倍數</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>評分</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>評分理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>8.41 / 2.13 = 3.95x</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>3.95x</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>YoY轉虧為盈+1435%、Q1累計達成率395%、本業強勁</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>📊 觀察重點</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>• 共 3 檔有 2026Q1 EPS 資料；其中 +8 以上 1 檔、+6~7 2 檔、+4~5 0 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>• 2026Q1 EPS 最高三名：雙鴻 12.61、南亞科 8.41、均華 5.19</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>• 已確認 2026Q1 一季賺贏 2025 全年 1 檔（含虧轉盈）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>資料來源</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>FinMind API + Anthropic Claude Haiku</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>產出時間</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-07 23:03:35</t>
+          <t>2026Q1 EPS 最高三名：雙鴻 12.61、南亞科 8.41、均華 5.19</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>已確認 2026Q1 一季賺贏 2025 全年 1 檔：南亞科</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>高分但尚未贏全年（達成率參考）：雙鴻 (45%)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="9" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>📑 工作表索引</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>摘要</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>本頁 — 重點摘要 + 已贏全年清單 + 觀察 + 索引</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>今日新公告</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>3 檔今日新公告（依分數排序）</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026Q1贏全年確認</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>已驗證 2026Q1 賺贏 2025 全年（1 檔）</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>2026Q1高EPS排行</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>2026Q1 EPS 前 30 名</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>高分排行</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>評分 ≥ 4（4 檔）</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>完整 EPS</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>全市場 5 檔依分數排序</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>月營收</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>最新月營收 + YoY + 累計</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>註：所有 EPS / 營收資料來自 FinMind API；驚喜度評分由 Anthropic Claude Haiku 4.5 依「驚喜度 / 延續性 / 獲利品質」三維度產出（範圍 -9 ~ +9）。達成率 = 今年累計 EPS / 去年全年 EPS。「上季 EPS」指最近一季之前那季（例如本期 Q1 → 上季 = 去年 Q4）。產出時間：2026-05-07 23:15:18</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A13:F13"/>
+  <mergeCells count="24">
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="C21:F21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -824,7 +943,7 @@
     <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>🆕 今日新公告 (3 檔)</t>
@@ -832,332 +951,332 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>最新季</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>去年同季</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>YoY %</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>YoY Δ</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>累計 EPS</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>去年全年</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>達成率</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>QoQ %</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>評分</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>級別</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>評分理由</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>GM%</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>OPM%</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>業外%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="5" t="n">
         <v>8.41</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="5" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>+1434.9%</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="5" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="5" t="n">
         <v>8.41</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="5" t="n">
         <v>2.13</v>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>394.8%</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>+134.9%</t>
         </is>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
-        <is>
-          <t>YoY轉虧為盈+1435%、Q1累計達成率395%、本業強勁</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>YoY+1435%轉虧為盈、Q1一季賺贏全年4倍、本業驅動毛利67.9%</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>67.9%</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>61.3%</t>
         </is>
       </c>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>6.2%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>3324</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="14" t="n">
         <v>12.61</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="14" t="n">
         <v>5.66</v>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>+122.8%</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="H4" s="14" t="n">
         <v>6.95</v>
       </c>
-      <c r="I4" s="13" t="n">
+      <c r="I4" s="14" t="n">
         <v>12.61</v>
       </c>
-      <c r="J4" s="13" t="n">
+      <c r="J4" s="14" t="n">
         <v>28.2</v>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>+24.5%</t>
         </is>
       </c>
-      <c r="M4" s="13" t="n">
+      <c r="M4" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="N4" s="13" t="inlineStr">
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
-        <is>
-          <t>YoY大增+123%、本業驅動穩健但累計進度正常</t>
-        </is>
-      </c>
-      <c r="P4" s="13" t="inlineStr">
+      <c r="O4" s="15" t="inlineStr">
+        <is>
+          <t>YoY 大幅成長+123%、本業穩健驅動、單季表現超預期</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>29.7%</t>
         </is>
       </c>
-      <c r="Q4" s="13" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>17.8%</t>
         </is>
       </c>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>均華</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="14" t="n">
         <v>5.19</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="14" t="n">
         <v>1.64</v>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>+216.5%</t>
         </is>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="14" t="n">
         <v>3.55</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="14" t="n">
         <v>5.19</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>12.75</v>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>40.7%</t>
         </is>
       </c>
-      <c r="L5" s="13" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>+54.9%</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="N5" s="13" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O5" s="14" t="inlineStr">
-        <is>
-          <t>YoY大增216%、本業驅動但累計進度正常</t>
-        </is>
-      </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="O5" s="15" t="inlineStr">
+        <is>
+          <t>YoY 大幅成長+216%、本業驅動強勁、累計進度正常</t>
+        </is>
+      </c>
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t>44.9%</t>
         </is>
       </c>
-      <c r="Q5" s="13" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>21.7%</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>4.7%</t>
         </is>
@@ -1191,93 +1310,93 @@
     <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>🏆 已確認 2026Q1 EPS &gt; 2025 全年 EPS (1 檔)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>一季賺贏去年全年的明星標的（含去年虧損 → 今年轉盈）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>2026Q1 EPS</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>2025Q1 EPS</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>2025 全年 EPS</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>累計/全年</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>倍數</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>評分</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="5" t="n">
         <v>8.41</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="5" t="n">
         <v>-0.63</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="5" t="n">
         <v>2.13</v>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>394.8%</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>3.95x</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1311,7 +1430,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>💰 2026Q1 EPS 高低排行（前 3 名）</t>
@@ -1319,159 +1438,159 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>依當期 EPS 由高到低；達成率 ≥ 100% 整列鮮黃高亮（已贏全年）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>評分</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>2026Q1 EPS</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>上季 EPS</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>QoQ Δ</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>去年全年 EPS</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>達成率</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>3324</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>12.61</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>10.13</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="18" t="n">
         <v>2.48</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="18" t="n">
         <v>28.2</v>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="5" t="n">
         <v>8.41</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="5" t="n">
         <v>3.58</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="5" t="n">
         <v>4.83</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="5" t="n">
         <v>2.13</v>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>395%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>均華</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>5.19</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>3.35</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <v>1.84</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="18" t="n">
         <v>12.75</v>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -1516,500 +1635,500 @@
     <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>🔥 高分排行 (評分 ≥ 4，5 檔)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>最新季</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>去年同季</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>YoY %</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>YoY Δ</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>累計 EPS</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>去年全年</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>達成率</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>QoQ %</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>評分</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>級別</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>評分理由</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>GM%</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>OPM%</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>業外%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>5386</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2025Q4</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="5" t="n">
         <v>5.58</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="5" t="n">
         <v>1.83</v>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>+204.9%</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="5" t="n">
         <v>3.75</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="5" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>258.2%</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>+758.5%</t>
         </is>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>QoQ 爆發 +758%、YoY 爆發 +205%、已賺贏去年全年 (258%)</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>13.4%</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>10.4%</t>
         </is>
       </c>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>-6.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="5" t="n">
         <v>8.41</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="5" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>+1434.9%</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="5" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="5" t="n">
         <v>8.41</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="J4" s="5" t="n">
         <v>2.13</v>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>394.8%</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>+134.9%</t>
         </is>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>YoY轉虧為盈+1435%、Q1累計達成率395%、本業強勁</t>
-        </is>
-      </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>YoY+1435%轉虧為盈、Q1一季賺贏全年4倍、本業驅動毛利67.9%</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>67.9%</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>61.3%</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>6.2%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>3324</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="14" t="n">
         <v>12.61</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="14" t="n">
         <v>5.66</v>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>+122.8%</t>
         </is>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="14" t="n">
         <v>6.95</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="14" t="n">
         <v>12.61</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>28.2</v>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="L5" s="13" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>+24.5%</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="N5" s="13" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O5" s="14" t="inlineStr">
-        <is>
-          <t>YoY大增+123%、本業驅動穩健但累計進度正常</t>
-        </is>
-      </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="O5" s="15" t="inlineStr">
+        <is>
+          <t>YoY 大幅成長+123%、本業穩健驅動、單季表現超預期</t>
+        </is>
+      </c>
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t>29.7%</t>
         </is>
       </c>
-      <c r="Q5" s="13" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>17.8%</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>均華</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>5.19</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="14" t="n">
         <v>1.64</v>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>+216.5%</t>
         </is>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="14" t="n">
         <v>3.55</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="14" t="n">
         <v>5.19</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="14" t="n">
         <v>12.75</v>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>40.7%</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>+54.9%</t>
         </is>
       </c>
-      <c r="M6" s="13" t="n">
+      <c r="M6" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="N6" s="13" t="inlineStr">
+      <c r="N6" s="14" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O6" s="14" t="inlineStr">
-        <is>
-          <t>YoY大增216%、本業驅動但累計進度正常</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>YoY 大幅成長+216%、本業驅動強勁、累計進度正常</t>
+        </is>
+      </c>
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t>44.9%</t>
         </is>
       </c>
-      <c r="Q6" s="13" t="inlineStr">
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t>21.7%</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>4.7%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>2330</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>2025Q4</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>19.51</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="14" t="n">
         <v>14.45</v>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>+35.0%</t>
         </is>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="14" t="n">
         <v>5.06</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="14" t="n">
         <v>66.26000000000001</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>45.26</v>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>146.4%</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t>+11.9%</t>
         </is>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="13" t="inlineStr">
+      <c r="N7" s="14" t="inlineStr">
         <is>
           <t>有亮點待觀察</t>
         </is>
       </c>
-      <c r="O7" s="14" t="inlineStr">
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>YoY +35%、已賺贏去年全年 (146%)、OPM 54% 強</t>
         </is>
       </c>
-      <c r="P7" s="13" t="inlineStr">
+      <c r="P7" s="14" t="inlineStr">
         <is>
           <t>62.3%</t>
         </is>
       </c>
-      <c r="Q7" s="13" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t>54.0%</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t>5.4%</t>
         </is>
@@ -2053,7 +2172,7 @@
     <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>📊 完整 EPS 全市場 (5 檔)</t>
@@ -2061,492 +2180,492 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>最新季</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>去年同季</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>YoY %</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>YoY Δ</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>累計 EPS</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>去年全年</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>達成率</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>QoQ %</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>評分</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>級別</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>評分理由</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>GM%</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>OPM%</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>業外%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>5386</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2025Q4</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="5" t="n">
         <v>5.58</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="5" t="n">
         <v>1.83</v>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>+204.9%</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="5" t="n">
         <v>3.75</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="5" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>258.2%</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>+758.5%</t>
         </is>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>QoQ 爆發 +758%、YoY 爆發 +205%、已賺贏去年全年 (258%)</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>13.4%</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>10.4%</t>
         </is>
       </c>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>-6.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="5" t="n">
         <v>8.41</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="5" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>+1434.9%</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="5" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="5" t="n">
         <v>8.41</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="J4" s="5" t="n">
         <v>2.13</v>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>394.8%</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>+134.9%</t>
         </is>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>高度超預期</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>YoY轉虧為盈+1435%、Q1累計達成率395%、本業強勁</t>
-        </is>
-      </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>YoY+1435%轉虧為盈、Q1一季賺贏全年4倍、本業驅動毛利67.9%</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>67.9%</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>61.3%</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>6.2%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>3324</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="14" t="n">
         <v>12.61</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="14" t="n">
         <v>5.66</v>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>+122.8%</t>
         </is>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="14" t="n">
         <v>6.95</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="14" t="n">
         <v>12.61</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>28.2</v>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="L5" s="13" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>+24.5%</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="N5" s="13" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O5" s="14" t="inlineStr">
-        <is>
-          <t>YoY大增+123%、本業驅動穩健但累計進度正常</t>
-        </is>
-      </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="O5" s="15" t="inlineStr">
+        <is>
+          <t>YoY 大幅成長+123%、本業穩健驅動、單季表現超預期</t>
+        </is>
+      </c>
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t>29.7%</t>
         </is>
       </c>
-      <c r="Q5" s="13" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>17.8%</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>4.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>均華</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>tpex</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>2026Q1</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>5.19</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="14" t="n">
         <v>1.64</v>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>+216.5%</t>
         </is>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="14" t="n">
         <v>3.55</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="14" t="n">
         <v>5.19</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="14" t="n">
         <v>12.75</v>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>40.7%</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>+54.9%</t>
         </is>
       </c>
-      <c r="M6" s="13" t="n">
+      <c r="M6" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="N6" s="13" t="inlineStr">
+      <c r="N6" s="14" t="inlineStr">
         <is>
           <t>值得關注</t>
         </is>
       </c>
-      <c r="O6" s="14" t="inlineStr">
-        <is>
-          <t>YoY大增216%、本業驅動但累計進度正常</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>YoY 大幅成長+216%、本業驅動強勁、累計進度正常</t>
+        </is>
+      </c>
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t>44.9%</t>
         </is>
       </c>
-      <c r="Q6" s="13" t="inlineStr">
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t>21.7%</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>4.7%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>2330</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>twse</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>2025Q4</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>19.51</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="14" t="n">
         <v>14.45</v>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>+35.0%</t>
         </is>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="14" t="n">
         <v>5.06</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="14" t="n">
         <v>66.26000000000001</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>45.26</v>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>146.4%</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t>+11.9%</t>
         </is>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="13" t="inlineStr">
+      <c r="N7" s="14" t="inlineStr">
         <is>
           <t>有亮點待觀察</t>
         </is>
       </c>
-      <c r="O7" s="14" t="inlineStr">
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>YoY +35%、已賺贏去年全年 (146%)、OPM 54% 強</t>
         </is>
       </c>
-      <c r="P7" s="13" t="inlineStr">
+      <c r="P7" s="14" t="inlineStr">
         <is>
           <t>62.3%</t>
         </is>
       </c>
-      <c r="Q7" s="13" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t>54.0%</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t>5.4%</t>
         </is>
